--- a/results/Int All Data -0.5/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_10_permute.xlsx
@@ -440,717 +440,717 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9022403062031537</v>
+        <v>0.8954297887129917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9022403062031537</v>
+        <v>0.8953534829940359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9098890726497282</v>
+        <v>0.8959379365299798</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9095714106421042</v>
+        <v>0.8914782292914447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9095459754024523</v>
+        <v>0.8887594435289408</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9069283736225053</v>
+        <v>0.8915042215071476</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.907347776588737</v>
+        <v>0.8923560235474621</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9042220269918021</v>
+        <v>0.897565791867704</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9058357722695733</v>
+        <v>0.8927878656454944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9000415504133876</v>
+        <v>0.893474060140046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8993174815473834</v>
+        <v>0.8959141722184801</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.871858376585618</v>
+        <v>0.8949611861956085</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8646538913688764</v>
+        <v>0.8949611861956085</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8553399521891758</v>
+        <v>0.8957480076966664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8520107206750253</v>
+        <v>0.8957480076966664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8607780806902344</v>
+        <v>0.8925205171411237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8604095482033066</v>
+        <v>0.8925205171411237</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8450345956391003</v>
+        <v>0.8925465093568263</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8427222167349766</v>
+        <v>0.8956846980855619</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.839761517707754</v>
+        <v>0.8957610038045177</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8517818035181577</v>
+        <v>0.895900619134578</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8527856600203334</v>
+        <v>0.8936515498415589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8546153263471208</v>
+        <v>0.8939692118491828</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8539291318525692</v>
+        <v>0.8939692118491828</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.855682492460401</v>
+        <v>0.8939692118491828</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8539291318525692</v>
+        <v>0.8958497486552741</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8539800023318731</v>
+        <v>0.8924572075300192</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8533955487959292</v>
+        <v>0.8833597463753855</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8509814289331978</v>
+        <v>0.8833597463753855</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8509814289331978</v>
+        <v>0.8842109914396494</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.849787086621658</v>
+        <v>0.8825848070300775</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8407156176827271</v>
+        <v>0.881796871576918</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8362174790966888</v>
+        <v>0.8859649090235319</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8347309100171771</v>
+        <v>0.8844020342250644</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8347309100171771</v>
+        <v>0.885863168064924</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8348829644790381</v>
+        <v>0.881454331305693</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8335614459692386</v>
+        <v>0.862878994353748</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8015939911938373</v>
+        <v>0.8602105220944973</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.784553865896505</v>
+        <v>0.8589528701718531</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7908822277853815</v>
+        <v>0.8519513098962762</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8065239718779078</v>
+        <v>0.846677674988879</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8043003378245406</v>
+        <v>0.8473384342437787</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8048847913604845</v>
+        <v>0.8425610649976198</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7993573610326188</v>
+        <v>0.8406296577122245</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7993573610326188</v>
+        <v>0.8413282913385769</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8076035771229885</v>
+        <v>0.8401209529191858</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7998909440892588</v>
+        <v>0.8407817121740855</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7861043015631719</v>
+        <v>0.8581394994790417</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7859901214727636</v>
+        <v>0.8578727079507218</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7969178059302354</v>
+        <v>0.8627133868079851</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7954182407428724</v>
+        <v>0.8623448543210573</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7895477131677306</v>
+        <v>0.8623448543210573</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7882640690293838</v>
+        <v>0.8623448543210573</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7885822880130585</v>
+        <v>0.8609215948526501</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7882900612450865</v>
+        <v>0.8581643777426429</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7824969533410022</v>
+        <v>0.8587997017578907</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7921658719237283</v>
+        <v>0.8587997017578907</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7904125113158967</v>
+        <v>0.8579230214539748</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.788392359179745</v>
+        <v>0.857020905910407</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7885704058573086</v>
+        <v>0.8551024947328631</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7691037215654444</v>
+        <v>0.8558519988385194</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7541866033149729</v>
+        <v>0.8597018173014584</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7473376544773076</v>
+        <v>0.8460818962732362</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7448477858716712</v>
+        <v>0.8460943354050368</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7347713464784632</v>
+        <v>0.8325388379400204</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7206286105972491</v>
+        <v>0.826998968480354</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7206286105972491</v>
+        <v>0.822423967199309</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7231444714185883</v>
+        <v>0.8308991004465462</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6894836237901552</v>
+        <v>0.8289298187896985</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6467761854863924</v>
+        <v>0.8267061847363313</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6370304042086596</v>
+        <v>0.8318385333855158</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6331410404461155</v>
+        <v>0.8296284524160507</v>
       </c>
     </row>
     <row r="74">
@@ -1160,803 +1160,803 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6220483054189314</v>
+        <v>0.8284719844759636</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6275503005071452</v>
+        <v>0.8278875309400195</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6511465908981202</v>
+        <v>0.7857938802442079</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6396090176650524</v>
+        <v>0.7828840516962892</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6402952121596042</v>
+        <v>0.7704590299556573</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6399521149123282</v>
+        <v>0.7466349363599165</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6409051009351999</v>
+        <v>0.745554774138785</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6556198512205573</v>
+        <v>0.752632083157267</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.64010472635024</v>
+        <v>0.7515643600679363</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6409814066541557</v>
+        <v>0.7532668501964641</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6414771153393433</v>
+        <v>0.7531396739982044</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6297869306683638</v>
+        <v>0.765795283823856</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6286943293154319</v>
+        <v>0.7642702833968409</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6342212026672469</v>
+        <v>0.7655663666669885</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.644005415292483</v>
+        <v>0.7657568524763527</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6440562857717869</v>
+        <v>0.758642226062469</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6380461428665849</v>
+        <v>0.7607262447857759</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5198990833659474</v>
+        <v>0.7614378745199795</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5178659351219443</v>
+        <v>0.7444892789536575</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5187171801862082</v>
+        <v>0.7444384084743535</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.511601439820223</v>
+        <v>0.7444129732347016</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5207124540587588</v>
+        <v>0.7433712423610734</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5180948522788118</v>
+        <v>0.7509182678490403</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5214873934040668</v>
+        <v>0.5682154561596724</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5273957953506609</v>
+        <v>0.5664112250725368</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5165314205042936</v>
+        <v>0.5677451827141369</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5150572905565824</v>
+        <v>0.5730674601966348</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5137612072864349</v>
+        <v>0.6542296389978293</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5140788692940589</v>
+        <v>0.6542296389978293</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5140788692940589</v>
+        <v>0.6531754689924006</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5052097683202419</v>
+        <v>0.6619801464030115</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5045744443049941</v>
+        <v>0.664978162825636</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5045744443049941</v>
+        <v>0.6230863231188877</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5021348892026108</v>
+        <v>0.6321199176863661</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5038882498104424</v>
+        <v>0.6301376399216669</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5054765598485619</v>
+        <v>0.6390564974226861</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5064041106317817</v>
+        <v>0.6350551814739369</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5035451525631667</v>
+        <v>0.6418532598322982</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5035451525631667</v>
+        <v>0.6345204844651953</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5035451525631667</v>
+        <v>0.6235046121330178</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5032020553158908</v>
+        <v>0.6234537416537138</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.502566731300643</v>
+        <v>0.5814731570962091</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5038373793311386</v>
+        <v>0.5976061540655168</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5035197173235146</v>
+        <v>0.5564270580450734</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5035451525631667</v>
+        <v>0.5410379954209142</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5035451525631667</v>
+        <v>0.5449776726867114</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5035451525631667</v>
+        <v>0.5425280920154141</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5045235738256902</v>
+        <v>0.5460602484707294</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5054765598485619</v>
+        <v>0.5087474945360649</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5044727033463864</v>
+        <v>0.5087474945360649</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5047903653540102</v>
+        <v>0.5045800140655019</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5045235738256902</v>
+        <v>0.4941870266167716</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5042059118180664</v>
+        <v>0.4949365307224277</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5022366301612186</v>
+        <v>0.4831717112606447</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5022366301612186</v>
+        <v>0.4830671854217831</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5018426624346388</v>
+        <v>0.4780371347072571</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5021348892026108</v>
+        <v>0.4776431669806774</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5021094539629588</v>
+        <v>0.4666007454567464</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5021094539629588</v>
+        <v>0.4894295228497568</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5021094539629588</v>
+        <v>0.4897726200970327</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5021094539629588</v>
+        <v>0.4865835608889932</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5021094539629588</v>
+        <v>0.4921358694804602</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.501474129947711</v>
+        <v>0.4921358694804602</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4997586437113319</v>
+        <v>0.499707773232028</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4997586437113319</v>
+        <v>0.5003430972472758</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4994918521830119</v>
+        <v>0.5003430972472758</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4995681579019677</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.49919962541504</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.49919962541504</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.49919962541504</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4989328338867199</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4989328338867199</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4982975098714722</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.498907398647068</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.499707773232028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.499707773232028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.499707773232028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5000254352396519</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.499707773232028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.499707773232028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
